--- a/Config/Table/Item.xlsx
+++ b/Config/Table/Item.xlsx
@@ -1,40 +1,468 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>图标地址</t>
+  </si>
+  <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>Ingredient</t>
+  </si>
+  <si>
+    <t>一个普通的苹果。</t>
+  </si>
+  <si>
+    <t>Items/apple</t>
+  </si>
+  <si>
+    <t>蘑菇</t>
+  </si>
+  <si>
+    <t>潮湿洞穴里长出的蘑菇。</t>
+  </si>
+  <si>
+    <t>Items/mushroom</t>
+  </si>
+  <si>
+    <t>矿石</t>
+  </si>
+  <si>
+    <t>沉甸甸的矿石。</t>
+  </si>
+  <si>
+    <t>Items/ore</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +470,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,176 +1058,125 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="12.2909090909091" customWidth="1"/>
+    <col min="2" max="2" width="13.1454545454545" customWidth="1"/>
+    <col min="4" max="4" width="34.4" customWidth="1"/>
+    <col min="5" max="5" width="41.4" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>图标地址</t>
-        </is>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>1001</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ingredient</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>一个普通的苹果。</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Items/apple</t>
-        </is>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>1002</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>蘑菇</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ingredient</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>潮湿洞穴里长出的蘑菇。</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Items/mushroom</t>
-        </is>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>1003</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>矿石</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ingredient</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>沉甸甸的矿石。</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Items/ore</t>
-        </is>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Table/Item.xlsx
+++ b/Config/Table/Item.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Item" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -22,160 +29,955 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ItemType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物品id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名称</t>
-  </si>
-  <si>
-    <t xml:space="preserve">类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">描述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">图标地址</t>
-  </si>
-  <si>
-    <t xml:space="preserve">测试物品</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingredient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是一个测试物品</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon_Test</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>物品id</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>图标地址</t>
+  </si>
+  <si>
+    <t>测试物品</t>
+  </si>
+  <si>
+    <t>Ingredient</t>
+  </si>
+  <si>
+    <t>这是一个测试物品</t>
+  </si>
+  <si>
+    <t>icon_item_10001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="0"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans SC"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="9">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -217,7 +1019,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -251,7 +1053,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -285,7 +1087,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -309,7 +1111,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -330,7 +1132,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -381,7 +1183,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -399,31 +1201,30 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="41.4"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="9"/>
+    <col min="1" max="1" width="12.2909090909091" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1454545454545" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.0181818181818" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.4" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +1241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -457,7 +1258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -474,8 +1275,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
         <v>10001</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -492,12 +1293,8 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Table/Item.xlsx
+++ b/Config/Table/Item.xlsx
@@ -77,7 +77,7 @@
     <t>这是一个测试物品</t>
   </si>
   <si>
-    <t>icon_item_10001</t>
+    <t>Icon_Item_10001</t>
   </si>
 </sst>
 </file>
